--- a/output/graficos_nacionales/plot_nacional_e_rezmat_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezmat_a_2022.xlsx
@@ -76,12 +76,6 @@
     <t xml:space="preserve">Tortel</t>
   </si>
   <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11102</t>
   </si>
   <si>
@@ -100,12 +94,6 @@
     <t xml:space="preserve">Cochrane</t>
   </si>
   <si>
-    <t xml:space="preserve">11101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
     <t xml:space="preserve">11202</t>
   </si>
   <si>
@@ -841,6 +829,12 @@
     <t xml:space="preserve">Rauco</t>
   </si>
   <si>
+    <t xml:space="preserve">6204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">6305</t>
   </si>
   <si>
@@ -1306,6 +1300,12 @@
     <t xml:space="preserve">Ovalle</t>
   </si>
   <si>
+    <t xml:space="preserve">4105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiguano</t>
+  </si>
+  <si>
     <t xml:space="preserve">3304</t>
   </si>
   <si>
@@ -2029,7 +2029,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:26</t>
+    <t xml:space="preserve">2026-09-09 20:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2573,7 +2573,7 @@
         <v>15</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5.5</v>
+        <v>5.11</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>15</v>
@@ -2605,7 +2605,7 @@
         <v>15</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>5.11</v>
+        <v>4.35</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>15</v>
@@ -2637,7 +2637,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>15</v>
@@ -2669,7 +2669,7 @@
         <v>15</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>4.3</v>
+        <v>4.13</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>15</v>
@@ -2701,7 +2701,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>4.23</v>
+        <v>3.77</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>15</v>
@@ -2712,10 +2712,10 @@
         <v>2022</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>29</v>
@@ -2733,7 +2733,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>4.13</v>
+        <v>2.61</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>15</v>
@@ -2744,10 +2744,10 @@
         <v>2022</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>31</v>
@@ -2765,7 +2765,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3.77</v>
+        <v>2.56</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>15</v>
@@ -2797,7 +2797,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2.61</v>
+        <v>2.43</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>15</v>
@@ -2829,7 +2829,7 @@
         <v>15</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>15</v>
@@ -2861,7 +2861,7 @@
         <v>15</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>2.43</v>
+        <v>1.79</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>15</v>
@@ -2872,10 +2872,10 @@
         <v>2022</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>39</v>
@@ -2893,7 +2893,7 @@
         <v>15</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2.35</v>
+        <v>1.54</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>15</v>
@@ -2925,7 +2925,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1.79</v>
+        <v>1.16</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>15</v>
@@ -2936,28 +2936,28 @@
         <v>2022</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1.54</v>
+        <v>4.88</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>15</v>
@@ -2968,28 +2968,28 @@
         <v>2022</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1.16</v>
+        <v>4.84</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>15</v>
@@ -3000,28 +3000,28 @@
         <v>2022</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>4.88</v>
+        <v>4.78</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>15</v>
@@ -3032,28 +3032,28 @@
         <v>2022</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>4.84</v>
+        <v>4.67</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>15</v>
@@ -3064,10 +3064,10 @@
         <v>2022</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>56</v>
@@ -3076,16 +3076,16 @@
         <v>57</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>4.78</v>
+        <v>4.56</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>15</v>
@@ -3096,28 +3096,28 @@
         <v>2022</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>4.67</v>
+        <v>4.47</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>15</v>
@@ -3128,28 +3128,28 @@
         <v>2022</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>4.56</v>
+        <v>4.33</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>15</v>
@@ -3163,7 +3163,7 @@
         <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>63</v>
@@ -3172,16 +3172,16 @@
         <v>64</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>4.47</v>
+        <v>4.3</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>15</v>
@@ -3192,10 +3192,10 @@
         <v>2022</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>65</v>
@@ -3204,16 +3204,16 @@
         <v>66</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>15</v>
@@ -3227,7 +3227,7 @@
         <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>67</v>
@@ -3236,16 +3236,16 @@
         <v>68</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>4.3</v>
+        <v>4.08</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>15</v>
@@ -3259,7 +3259,7 @@
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>69</v>
@@ -3268,16 +3268,16 @@
         <v>70</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>4.1</v>
+        <v>4.07</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>15</v>
@@ -3288,10 +3288,10 @@
         <v>2022</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>71</v>
@@ -3300,16 +3300,16 @@
         <v>72</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>15</v>
@@ -3320,10 +3320,10 @@
         <v>2022</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>73</v>
@@ -3332,16 +3332,16 @@
         <v>74</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>15</v>
@@ -3355,7 +3355,7 @@
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>75</v>
@@ -3364,16 +3364,16 @@
         <v>76</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>15</v>
@@ -3384,10 +3384,10 @@
         <v>2022</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>77</v>
@@ -3396,16 +3396,16 @@
         <v>78</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>15</v>
@@ -3416,10 +3416,10 @@
         <v>2022</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>79</v>
@@ -3428,16 +3428,16 @@
         <v>80</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>15</v>
@@ -3451,7 +3451,7 @@
         <v>13</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>81</v>
@@ -3460,16 +3460,16 @@
         <v>82</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>4.05</v>
+        <v>3.93</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>15</v>
@@ -3480,10 +3480,10 @@
         <v>2022</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>83</v>
@@ -3492,16 +3492,16 @@
         <v>84</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>3.94</v>
+        <v>3.81</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>15</v>
@@ -3512,10 +3512,10 @@
         <v>2022</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>85</v>
@@ -3524,16 +3524,16 @@
         <v>86</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>3.93</v>
+        <v>3.78</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>15</v>
@@ -3544,10 +3544,10 @@
         <v>2022</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>87</v>
@@ -3556,16 +3556,16 @@
         <v>88</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>15</v>
@@ -3576,10 +3576,10 @@
         <v>2022</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>89</v>
@@ -3588,16 +3588,16 @@
         <v>90</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>3.78</v>
+        <v>3.73</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>15</v>
@@ -3611,7 +3611,7 @@
         <v>13</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>91</v>
@@ -3620,16 +3620,16 @@
         <v>92</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>3.78</v>
+        <v>3.71</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>15</v>
@@ -3640,10 +3640,10 @@
         <v>2022</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>93</v>
@@ -3652,16 +3652,16 @@
         <v>94</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>15</v>
@@ -3675,7 +3675,7 @@
         <v>13</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>95</v>
@@ -3684,16 +3684,16 @@
         <v>96</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>15</v>
@@ -3707,7 +3707,7 @@
         <v>13</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>97</v>
@@ -3716,16 +3716,16 @@
         <v>98</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>15</v>
@@ -3736,10 +3736,10 @@
         <v>2022</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>99</v>
@@ -3748,16 +3748,16 @@
         <v>100</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>3.69</v>
+        <v>3.61</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>15</v>
@@ -3768,10 +3768,10 @@
         <v>2022</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>101</v>
@@ -3780,16 +3780,16 @@
         <v>102</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>15</v>
@@ -3800,10 +3800,10 @@
         <v>2022</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>103</v>
@@ -3812,16 +3812,16 @@
         <v>104</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>15</v>
@@ -3835,7 +3835,7 @@
         <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>105</v>
@@ -3844,16 +3844,16 @@
         <v>106</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>15</v>
@@ -3864,10 +3864,10 @@
         <v>2022</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>107</v>
@@ -3876,16 +3876,16 @@
         <v>108</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>3.59</v>
+        <v>3.53</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>15</v>
@@ -3899,7 +3899,7 @@
         <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>109</v>
@@ -3908,16 +3908,16 @@
         <v>110</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>15</v>
@@ -3928,10 +3928,10 @@
         <v>2022</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>111</v>
@@ -3940,16 +3940,16 @@
         <v>112</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>3.53</v>
+        <v>3.43</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>15</v>
@@ -3960,10 +3960,10 @@
         <v>2022</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>113</v>
@@ -3972,16 +3972,16 @@
         <v>114</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>15</v>
@@ -3992,10 +3992,10 @@
         <v>2022</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>115</v>
@@ -4004,16 +4004,16 @@
         <v>116</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>15</v>
@@ -4024,10 +4024,10 @@
         <v>2022</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>117</v>
@@ -4036,16 +4036,16 @@
         <v>118</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>15</v>
@@ -4056,10 +4056,10 @@
         <v>2022</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>119</v>
@@ -4068,16 +4068,16 @@
         <v>120</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>15</v>
@@ -4088,10 +4088,10 @@
         <v>2022</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>121</v>
@@ -4100,16 +4100,16 @@
         <v>122</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>15</v>
@@ -4120,10 +4120,10 @@
         <v>2022</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>123</v>
@@ -4132,16 +4132,16 @@
         <v>124</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>15</v>
@@ -4152,10 +4152,10 @@
         <v>2022</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>125</v>
@@ -4164,16 +4164,16 @@
         <v>126</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>3.37</v>
+        <v>3.31</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>15</v>
@@ -4187,7 +4187,7 @@
         <v>13</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>127</v>
@@ -4196,16 +4196,16 @@
         <v>128</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>3.34</v>
+        <v>3.29</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>15</v>
@@ -4216,10 +4216,10 @@
         <v>2022</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>129</v>
@@ -4228,16 +4228,16 @@
         <v>130</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>15</v>
@@ -4248,10 +4248,10 @@
         <v>2022</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>131</v>
@@ -4260,16 +4260,16 @@
         <v>132</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>15</v>
@@ -4280,10 +4280,10 @@
         <v>2022</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>133</v>
@@ -4292,16 +4292,16 @@
         <v>134</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>15</v>
@@ -4312,10 +4312,10 @@
         <v>2022</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>135</v>
@@ -4324,16 +4324,16 @@
         <v>136</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>15</v>
@@ -4344,28 +4344,28 @@
         <v>2022</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>62</v>
+        <v>137</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>15</v>
@@ -4376,28 +4376,28 @@
         <v>2022</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>15</v>
@@ -4408,10 +4408,10 @@
         <v>2022</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>142</v>
@@ -4420,16 +4420,16 @@
         <v>143</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>15</v>
@@ -4440,10 +4440,10 @@
         <v>2022</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>144</v>
@@ -4452,16 +4452,16 @@
         <v>145</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>3.24</v>
+        <v>3.19</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>15</v>
@@ -4475,7 +4475,7 @@
         <v>7</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>146</v>
@@ -4484,16 +4484,16 @@
         <v>147</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>3.24</v>
+        <v>3.19</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>15</v>
@@ -4504,10 +4504,10 @@
         <v>2022</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>148</v>
@@ -4516,16 +4516,16 @@
         <v>149</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>15</v>
@@ -4536,10 +4536,10 @@
         <v>2022</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>150</v>
@@ -4548,16 +4548,16 @@
         <v>151</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>15</v>
@@ -4571,7 +4571,7 @@
         <v>6</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>152</v>
@@ -4580,16 +4580,16 @@
         <v>153</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>15</v>
@@ -4603,7 +4603,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>154</v>
@@ -4612,16 +4612,16 @@
         <v>155</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>15</v>
@@ -4632,10 +4632,10 @@
         <v>2022</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>156</v>
@@ -4644,16 +4644,16 @@
         <v>157</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>15</v>
@@ -4664,10 +4664,10 @@
         <v>2022</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>158</v>
@@ -4676,16 +4676,16 @@
         <v>159</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>15</v>
@@ -4696,10 +4696,10 @@
         <v>2022</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>160</v>
@@ -4708,16 +4708,16 @@
         <v>161</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>15</v>
@@ -4728,10 +4728,10 @@
         <v>2022</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>162</v>
@@ -4740,16 +4740,16 @@
         <v>163</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>15</v>
@@ -4760,10 +4760,10 @@
         <v>2022</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>164</v>
@@ -4772,16 +4772,16 @@
         <v>165</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>15</v>
@@ -4792,10 +4792,10 @@
         <v>2022</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>166</v>
@@ -4804,16 +4804,16 @@
         <v>167</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>15</v>
@@ -4824,10 +4824,10 @@
         <v>2022</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>168</v>
@@ -4836,16 +4836,16 @@
         <v>169</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>15</v>
@@ -4856,10 +4856,10 @@
         <v>2022</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>170</v>
@@ -4868,16 +4868,16 @@
         <v>171</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>3.11</v>
+        <v>3.07</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>15</v>
@@ -4888,10 +4888,10 @@
         <v>2022</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>172</v>
@@ -4900,16 +4900,16 @@
         <v>173</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>15</v>
@@ -4920,10 +4920,10 @@
         <v>2022</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>174</v>
@@ -4932,16 +4932,16 @@
         <v>175</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>15</v>
@@ -4952,10 +4952,10 @@
         <v>2022</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>176</v>
@@ -4964,16 +4964,16 @@
         <v>177</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>15</v>
@@ -4984,10 +4984,10 @@
         <v>2022</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>178</v>
@@ -4996,16 +4996,16 @@
         <v>179</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>15</v>
@@ -5016,10 +5016,10 @@
         <v>2022</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>62</v>
+        <v>137</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>180</v>
@@ -5028,16 +5028,16 @@
         <v>181</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>15</v>
@@ -5048,10 +5048,10 @@
         <v>2022</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>182</v>
@@ -5060,16 +5060,16 @@
         <v>183</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>15</v>
@@ -5080,10 +5080,10 @@
         <v>2022</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>184</v>
@@ -5092,16 +5092,16 @@
         <v>185</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>15</v>
@@ -5115,7 +5115,7 @@
         <v>13</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>186</v>
@@ -5124,16 +5124,16 @@
         <v>187</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>15</v>
@@ -5147,7 +5147,7 @@
         <v>5</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>188</v>
@@ -5156,16 +5156,16 @@
         <v>189</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>15</v>
@@ -5176,10 +5176,10 @@
         <v>2022</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>190</v>
@@ -5188,16 +5188,16 @@
         <v>191</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>15</v>
@@ -5211,7 +5211,7 @@
         <v>5</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>192</v>
@@ -5220,16 +5220,16 @@
         <v>193</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>15</v>
@@ -5240,10 +5240,10 @@
         <v>2022</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>194</v>
@@ -5252,16 +5252,16 @@
         <v>195</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>15</v>
@@ -5272,10 +5272,10 @@
         <v>2022</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>196</v>
@@ -5284,16 +5284,16 @@
         <v>197</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>15</v>
@@ -5304,10 +5304,10 @@
         <v>2022</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>198</v>
@@ -5316,16 +5316,16 @@
         <v>199</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>15</v>
@@ -5336,10 +5336,10 @@
         <v>2022</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>200</v>
@@ -5348,10 +5348,10 @@
         <v>201</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
@@ -5368,10 +5368,10 @@
         <v>2022</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>202</v>
@@ -5380,16 +5380,16 @@
         <v>203</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>15</v>
@@ -5403,7 +5403,7 @@
         <v>6</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>204</v>
@@ -5412,16 +5412,16 @@
         <v>205</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>15</v>
@@ -5432,10 +5432,10 @@
         <v>2022</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>206</v>
@@ -5444,16 +5444,16 @@
         <v>207</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>15</v>
@@ -5464,10 +5464,10 @@
         <v>2022</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>208</v>
@@ -5476,16 +5476,16 @@
         <v>209</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>15</v>
@@ -5496,10 +5496,10 @@
         <v>2022</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>210</v>
@@ -5508,16 +5508,16 @@
         <v>211</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>15</v>
@@ -5528,10 +5528,10 @@
         <v>2022</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>212</v>
@@ -5540,16 +5540,16 @@
         <v>213</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>15</v>
@@ -5560,10 +5560,10 @@
         <v>2022</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>214</v>
@@ -5572,16 +5572,16 @@
         <v>215</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>15</v>
@@ -5595,7 +5595,7 @@
         <v>13</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>216</v>
@@ -5604,16 +5604,16 @@
         <v>217</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>15</v>
@@ -5624,10 +5624,10 @@
         <v>2022</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>218</v>
@@ -5636,16 +5636,16 @@
         <v>219</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>15</v>
@@ -5656,10 +5656,10 @@
         <v>2022</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>220</v>
@@ -5668,16 +5668,16 @@
         <v>221</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>15</v>
@@ -5688,10 +5688,10 @@
         <v>2022</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>62</v>
+        <v>137</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>222</v>
@@ -5700,10 +5700,10 @@
         <v>223</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
@@ -5720,10 +5720,10 @@
         <v>2022</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>224</v>
@@ -5732,16 +5732,16 @@
         <v>225</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>15</v>
@@ -5752,10 +5752,10 @@
         <v>2022</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>226</v>
@@ -5764,16 +5764,16 @@
         <v>227</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>15</v>
@@ -5787,7 +5787,7 @@
         <v>5</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>228</v>
@@ -5796,16 +5796,16 @@
         <v>229</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>15</v>
@@ -5816,10 +5816,10 @@
         <v>2022</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>230</v>
@@ -5828,16 +5828,16 @@
         <v>231</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>15</v>
@@ -5848,10 +5848,10 @@
         <v>2022</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>232</v>
@@ -5860,16 +5860,16 @@
         <v>233</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>15</v>
@@ -5880,10 +5880,10 @@
         <v>2022</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>234</v>
@@ -5892,16 +5892,16 @@
         <v>235</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>15</v>
@@ -5912,10 +5912,10 @@
         <v>2022</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>236</v>
@@ -5924,16 +5924,16 @@
         <v>237</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>15</v>
@@ -5944,10 +5944,10 @@
         <v>2022</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>238</v>
@@ -5956,16 +5956,16 @@
         <v>239</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>15</v>
@@ -5976,10 +5976,10 @@
         <v>2022</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>62</v>
+        <v>137</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>240</v>
@@ -5988,16 +5988,16 @@
         <v>241</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>15</v>
@@ -6008,10 +6008,10 @@
         <v>2022</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>242</v>
@@ -6020,16 +6020,16 @@
         <v>243</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>15</v>
@@ -6040,10 +6040,10 @@
         <v>2022</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>244</v>
@@ -6052,16 +6052,16 @@
         <v>245</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>15</v>
@@ -6072,10 +6072,10 @@
         <v>2022</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>246</v>
@@ -6084,10 +6084,10 @@
         <v>247</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
@@ -6104,10 +6104,10 @@
         <v>2022</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>248</v>
@@ -6116,16 +6116,16 @@
         <v>249</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>15</v>
@@ -6136,10 +6136,10 @@
         <v>2022</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>250</v>
@@ -6148,16 +6148,16 @@
         <v>251</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>15</v>
@@ -6168,10 +6168,10 @@
         <v>2022</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>252</v>
@@ -6180,16 +6180,16 @@
         <v>253</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>15</v>
@@ -6200,10 +6200,10 @@
         <v>2022</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>254</v>
@@ -6212,16 +6212,16 @@
         <v>255</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>2.51</v>
+        <v>2.42</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>15</v>
@@ -6232,10 +6232,10 @@
         <v>2022</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>256</v>
@@ -6244,16 +6244,16 @@
         <v>257</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>15</v>
@@ -6267,7 +6267,7 @@
         <v>6</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>258</v>
@@ -6276,16 +6276,16 @@
         <v>259</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>15</v>
@@ -6296,10 +6296,10 @@
         <v>2022</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>260</v>
@@ -6308,16 +6308,16 @@
         <v>261</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>15</v>
@@ -6328,10 +6328,10 @@
         <v>2022</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>262</v>
@@ -6340,16 +6340,16 @@
         <v>263</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>15</v>
@@ -6360,10 +6360,10 @@
         <v>2022</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>264</v>
@@ -6372,16 +6372,16 @@
         <v>265</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>15</v>
@@ -6395,7 +6395,7 @@
         <v>7</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>266</v>
@@ -6404,16 +6404,16 @@
         <v>267</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>15</v>
@@ -6424,10 +6424,10 @@
         <v>2022</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>268</v>
@@ -6436,16 +6436,16 @@
         <v>269</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>15</v>
@@ -6456,10 +6456,10 @@
         <v>2022</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>270</v>
@@ -6468,16 +6468,16 @@
         <v>271</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>15</v>
@@ -6488,10 +6488,10 @@
         <v>2022</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>272</v>
@@ -6500,16 +6500,16 @@
         <v>273</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>15</v>
@@ -6520,10 +6520,10 @@
         <v>2022</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>274</v>
@@ -6532,16 +6532,16 @@
         <v>275</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>15</v>
@@ -6552,10 +6552,10 @@
         <v>2022</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>276</v>
@@ -6564,10 +6564,10 @@
         <v>277</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
@@ -6587,7 +6587,7 @@
         <v>7</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>278</v>
@@ -6596,16 +6596,16 @@
         <v>279</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>15</v>
@@ -6616,10 +6616,10 @@
         <v>2022</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>280</v>
@@ -6628,16 +6628,16 @@
         <v>281</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>15</v>
@@ -6648,10 +6648,10 @@
         <v>2022</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>282</v>
@@ -6660,16 +6660,16 @@
         <v>283</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>15</v>
@@ -6680,10 +6680,10 @@
         <v>2022</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>284</v>
@@ -6692,10 +6692,10 @@
         <v>285</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
@@ -6712,10 +6712,10 @@
         <v>2022</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>286</v>
@@ -6724,16 +6724,16 @@
         <v>287</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>15</v>
@@ -6744,10 +6744,10 @@
         <v>2022</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>288</v>
@@ -6756,10 +6756,10 @@
         <v>289</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
@@ -6776,10 +6776,10 @@
         <v>2022</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>290</v>
@@ -6788,10 +6788,10 @@
         <v>291</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
@@ -6808,10 +6808,10 @@
         <v>2022</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>292</v>
@@ -6820,16 +6820,16 @@
         <v>293</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>15</v>
@@ -6843,7 +6843,7 @@
         <v>5</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>294</v>
@@ -6852,10 +6852,10 @@
         <v>295</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
@@ -6875,7 +6875,7 @@
         <v>5</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>296</v>
@@ -6884,16 +6884,16 @@
         <v>297</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>15</v>
@@ -6904,10 +6904,10 @@
         <v>2022</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>298</v>
@@ -6916,10 +6916,10 @@
         <v>299</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
@@ -6939,7 +6939,7 @@
         <v>13</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>300</v>
@@ -6948,10 +6948,10 @@
         <v>301</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
@@ -6968,10 +6968,10 @@
         <v>2022</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>302</v>
@@ -6980,10 +6980,10 @@
         <v>303</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
@@ -7000,10 +7000,10 @@
         <v>2022</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>304</v>
@@ -7012,16 +7012,16 @@
         <v>305</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>15</v>
@@ -7032,10 +7032,10 @@
         <v>2022</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>306</v>
@@ -7044,16 +7044,16 @@
         <v>307</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>15</v>
@@ -7064,10 +7064,10 @@
         <v>2022</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>308</v>
@@ -7076,16 +7076,16 @@
         <v>309</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>15</v>
@@ -7096,10 +7096,10 @@
         <v>2022</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>310</v>
@@ -7108,16 +7108,16 @@
         <v>311</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>15</v>
@@ -7128,10 +7128,10 @@
         <v>2022</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>312</v>
@@ -7140,16 +7140,16 @@
         <v>313</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>15</v>
@@ -7163,7 +7163,7 @@
         <v>13</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>314</v>
@@ -7172,16 +7172,16 @@
         <v>315</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>15</v>
@@ -7192,10 +7192,10 @@
         <v>2022</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>316</v>
@@ -7204,16 +7204,16 @@
         <v>317</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>15</v>
@@ -7224,10 +7224,10 @@
         <v>2022</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>318</v>
@@ -7236,16 +7236,16 @@
         <v>319</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>15</v>
@@ -7256,10 +7256,10 @@
         <v>2022</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>320</v>
@@ -7268,10 +7268,10 @@
         <v>321</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
@@ -7288,10 +7288,10 @@
         <v>2022</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>322</v>
@@ -7300,16 +7300,16 @@
         <v>323</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>15</v>
@@ -7320,10 +7320,10 @@
         <v>2022</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>324</v>
@@ -7332,16 +7332,16 @@
         <v>325</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>15</v>
@@ -7352,10 +7352,10 @@
         <v>2022</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>326</v>
@@ -7364,10 +7364,10 @@
         <v>327</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
@@ -7384,10 +7384,10 @@
         <v>2022</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>328</v>
@@ -7396,10 +7396,10 @@
         <v>329</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
@@ -7416,10 +7416,10 @@
         <v>2022</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>330</v>
@@ -7428,16 +7428,16 @@
         <v>331</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>15</v>
@@ -7448,10 +7448,10 @@
         <v>2022</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>332</v>
@@ -7460,10 +7460,10 @@
         <v>333</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
@@ -7480,10 +7480,10 @@
         <v>2022</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>334</v>
@@ -7492,16 +7492,16 @@
         <v>335</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>15</v>
@@ -7512,10 +7512,10 @@
         <v>2022</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>336</v>
@@ -7524,16 +7524,16 @@
         <v>337</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>15</v>
@@ -7544,10 +7544,10 @@
         <v>2022</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>338</v>
@@ -7556,16 +7556,16 @@
         <v>339</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>15</v>
@@ -7576,10 +7576,10 @@
         <v>2022</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>340</v>
@@ -7588,16 +7588,16 @@
         <v>341</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>15</v>
@@ -7611,7 +7611,7 @@
         <v>16</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>342</v>
@@ -7620,16 +7620,16 @@
         <v>343</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>15</v>
@@ -7640,10 +7640,10 @@
         <v>2022</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>344</v>
@@ -7652,16 +7652,16 @@
         <v>345</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>15</v>
@@ -7675,7 +7675,7 @@
         <v>13</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>346</v>
@@ -7684,16 +7684,16 @@
         <v>347</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>15</v>
@@ -7704,10 +7704,10 @@
         <v>2022</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>348</v>
@@ -7716,16 +7716,16 @@
         <v>349</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>15</v>
@@ -7736,10 +7736,10 @@
         <v>2022</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>350</v>
@@ -7748,16 +7748,16 @@
         <v>351</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>15</v>
@@ -7768,10 +7768,10 @@
         <v>2022</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>352</v>
@@ -7780,16 +7780,16 @@
         <v>353</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>15</v>
@@ -7803,7 +7803,7 @@
         <v>6</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>354</v>
@@ -7812,16 +7812,16 @@
         <v>355</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>15</v>
@@ -7832,10 +7832,10 @@
         <v>2022</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>62</v>
+        <v>137</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>356</v>
@@ -7844,10 +7844,10 @@
         <v>357</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
@@ -7867,7 +7867,7 @@
         <v>16</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>358</v>
@@ -7876,16 +7876,16 @@
         <v>359</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>15</v>
@@ -7896,10 +7896,10 @@
         <v>2022</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>360</v>
@@ -7908,16 +7908,16 @@
         <v>361</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>15</v>
@@ -7928,10 +7928,10 @@
         <v>2022</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>362</v>
@@ -7940,16 +7940,16 @@
         <v>363</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>15</v>
@@ -7960,10 +7960,10 @@
         <v>2022</v>
       </c>
       <c r="B173" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>364</v>
@@ -7972,16 +7972,16 @@
         <v>365</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>1.2</v>
+        <v>0.98</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>15</v>
@@ -7992,10 +7992,10 @@
         <v>2022</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>366</v>
@@ -8004,16 +8004,16 @@
         <v>367</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>15</v>
@@ -8027,7 +8027,7 @@
         <v>13</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>368</v>
@@ -8036,16 +8036,16 @@
         <v>369</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>0.97</v>
+        <v>0.75</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>15</v>
@@ -8056,28 +8056,28 @@
         <v>2022</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>52</v>
+        <v>370</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>50</v>
+        <v>373</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>51</v>
+        <v>374</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>0.75</v>
+        <v>4.75</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>15</v>
@@ -8088,28 +8088,28 @@
         <v>2022</v>
       </c>
       <c r="B177" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D177" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F177" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="E177" s="2" t="s">
+      <c r="G177" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="F177" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="G177" s="2" t="s">
-        <v>376</v>
-      </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>4.75</v>
+        <v>4.68</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>15</v>
@@ -8120,10 +8120,10 @@
         <v>2022</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>378</v>
@@ -8132,16 +8132,16 @@
         <v>379</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>4.68</v>
+        <v>4.65</v>
       </c>
       <c r="J178" s="2" t="s">
         <v>15</v>
@@ -8152,28 +8152,28 @@
         <v>2022</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>4.65</v>
+        <v>4.44</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>15</v>
@@ -8187,7 +8187,7 @@
         <v>2</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>383</v>
@@ -8196,16 +8196,16 @@
         <v>384</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>4.44</v>
+        <v>4.35</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>15</v>
@@ -8216,28 +8216,28 @@
         <v>2022</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>4.35</v>
+        <v>4.31</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>15</v>
@@ -8248,10 +8248,10 @@
         <v>2022</v>
       </c>
       <c r="B182" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>388</v>
@@ -8260,16 +8260,16 @@
         <v>389</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>4.31</v>
+        <v>4.19</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>15</v>
@@ -8280,10 +8280,10 @@
         <v>2022</v>
       </c>
       <c r="B183" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>390</v>
@@ -8292,16 +8292,16 @@
         <v>391</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>4.19</v>
+        <v>3.61</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>15</v>
@@ -8312,10 +8312,10 @@
         <v>2022</v>
       </c>
       <c r="B184" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>392</v>
@@ -8324,16 +8324,16 @@
         <v>393</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>15</v>
@@ -8344,10 +8344,10 @@
         <v>2022</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>394</v>
@@ -8356,16 +8356,16 @@
         <v>395</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>3.56</v>
+        <v>3.46</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>15</v>
@@ -8376,10 +8376,10 @@
         <v>2022</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>396</v>
@@ -8388,16 +8388,16 @@
         <v>397</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>3.46</v>
+        <v>3.31</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>15</v>
@@ -8408,10 +8408,10 @@
         <v>2022</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>398</v>
@@ -8420,16 +8420,16 @@
         <v>399</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>3.31</v>
+        <v>3.09</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>15</v>
@@ -8440,10 +8440,10 @@
         <v>2022</v>
       </c>
       <c r="B188" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>400</v>
@@ -8452,16 +8452,16 @@
         <v>401</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>15</v>
@@ -8475,7 +8475,7 @@
         <v>3</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>402</v>
@@ -8484,16 +8484,16 @@
         <v>403</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>15</v>
@@ -8504,28 +8504,28 @@
         <v>2022</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>15</v>
@@ -8536,28 +8536,28 @@
         <v>2022</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>406</v>
+        <v>380</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>407</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>408</v>
+        <v>380</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>15</v>
@@ -8571,19 +8571,19 @@
         <v>2</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D192" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="E192" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="E192" s="2" t="s">
-        <v>382</v>
-      </c>
       <c r="F192" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
@@ -8600,10 +8600,10 @@
         <v>2022</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>410</v>
@@ -8612,10 +8612,10 @@
         <v>411</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
@@ -8632,10 +8632,10 @@
         <v>2022</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>412</v>
@@ -8644,16 +8644,16 @@
         <v>413</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>2.85</v>
+        <v>2.67</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>15</v>
@@ -8664,10 +8664,10 @@
         <v>2022</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>414</v>
@@ -8676,10 +8676,10 @@
         <v>415</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
@@ -8696,10 +8696,10 @@
         <v>2022</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>416</v>
@@ -8708,16 +8708,16 @@
         <v>417</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>15</v>
@@ -8728,28 +8728,28 @@
         <v>2022</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>418</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>419</v>
+        <v>385</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>15</v>
@@ -8763,25 +8763,25 @@
         <v>4</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D198" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E198" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="E198" s="2" t="s">
-        <v>387</v>
-      </c>
       <c r="F198" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>15</v>
@@ -8792,10 +8792,10 @@
         <v>2022</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>421</v>
@@ -8804,16 +8804,16 @@
         <v>422</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>2.58</v>
+        <v>2.41</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>15</v>
@@ -8824,10 +8824,10 @@
         <v>2022</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>423</v>
@@ -8836,16 +8836,16 @@
         <v>424</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>15</v>
@@ -8856,10 +8856,10 @@
         <v>2022</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>406</v>
+        <v>385</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>425</v>
@@ -8868,10 +8868,10 @@
         <v>426</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
@@ -8891,7 +8891,7 @@
         <v>4</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>427</v>
@@ -8900,16 +8900,16 @@
         <v>428</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>15</v>
@@ -8923,7 +8923,7 @@
         <v>3</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>429</v>
@@ -8932,10 +8932,10 @@
         <v>430</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
@@ -8955,7 +8955,7 @@
         <v>3</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>431</v>
@@ -8964,10 +8964,10 @@
         <v>432</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
@@ -8987,7 +8987,7 @@
         <v>4</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>433</v>
@@ -8996,10 +8996,10 @@
         <v>434</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
@@ -9019,7 +9019,7 @@
         <v>3</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>435</v>
@@ -9028,10 +9028,10 @@
         <v>436</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
@@ -9051,7 +9051,7 @@
         <v>4</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>437</v>
@@ -9060,10 +9060,10 @@
         <v>438</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
@@ -9083,7 +9083,7 @@
         <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>439</v>
@@ -9092,10 +9092,10 @@
         <v>440</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
@@ -9115,7 +9115,7 @@
         <v>4</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>441</v>
@@ -9124,10 +9124,10 @@
         <v>442</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
@@ -9147,7 +9147,7 @@
         <v>4</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>443</v>
@@ -9156,10 +9156,10 @@
         <v>444</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
@@ -9179,7 +9179,7 @@
         <v>2</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>445</v>
@@ -9188,10 +9188,10 @@
         <v>446</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
@@ -9211,7 +9211,7 @@
         <v>2</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>447</v>
@@ -9220,10 +9220,10 @@
         <v>448</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
@@ -9243,7 +9243,7 @@
         <v>4</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>449</v>
@@ -9252,10 +9252,10 @@
         <v>450</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9275,7 +9275,7 @@
         <v>1</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>451</v>
@@ -9284,10 +9284,10 @@
         <v>452</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>

--- a/output/graficos_nacionales/plot_nacional_e_rezmat_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezmat_a_2022.xlsx
@@ -316,18 +316,18 @@
     <t xml:space="preserve">Puente Alto</t>
   </si>
   <si>
+    <t xml:space="preserve">5701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Felipe</t>
+  </si>
+  <si>
     <t xml:space="preserve">5802</t>
   </si>
   <si>
     <t xml:space="preserve">Limache</t>
   </si>
   <si>
-    <t xml:space="preserve">5701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Felipe</t>
-  </si>
-  <si>
     <t xml:space="preserve">13129</t>
   </si>
   <si>
@@ -400,18 +400,18 @@
     <t xml:space="preserve">Panquehue</t>
   </si>
   <si>
+    <t xml:space="preserve">13401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Bernardo</t>
+  </si>
+  <si>
     <t xml:space="preserve">13603</t>
   </si>
   <si>
     <t xml:space="preserve">Isla de Maipo</t>
   </si>
   <si>
-    <t xml:space="preserve">13401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Bernardo</t>
-  </si>
-  <si>
     <t xml:space="preserve">6104</t>
   </si>
   <si>
@@ -613,18 +613,18 @@
     <t xml:space="preserve">Melipilla</t>
   </si>
   <si>
+    <t xml:space="preserve">6109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malloa</t>
+  </si>
+  <si>
     <t xml:space="preserve">6202</t>
   </si>
   <si>
     <t xml:space="preserve">La Estrella</t>
   </si>
   <si>
-    <t xml:space="preserve">6109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malloa</t>
-  </si>
-  <si>
     <t xml:space="preserve">5604</t>
   </si>
   <si>
@@ -1840,16 +1840,22 @@
     <t xml:space="preserve">Talcahuano</t>
   </si>
   <si>
+    <t xml:space="preserve">8301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Ángeles</t>
+  </si>
+  <si>
     <t xml:space="preserve">8302</t>
   </si>
   <si>
     <t xml:space="preserve">Antuco</t>
   </si>
   <si>
-    <t xml:space="preserve">8301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Ángeles</t>
+    <t xml:space="preserve">8105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualqui</t>
   </si>
   <si>
     <t xml:space="preserve">8303</t>
@@ -1858,12 +1864,6 @@
     <t xml:space="preserve">Cabrero</t>
   </si>
   <si>
-    <t xml:space="preserve">8105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualqui</t>
-  </si>
-  <si>
     <t xml:space="preserve">8312</t>
   </si>
   <si>
@@ -2029,7 +2029,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:19</t>
+    <t xml:space="preserve">2026-09-18 11:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_rezmat_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezmat_a_2022.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="688">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -67,7 +67,7 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">Aysen</t>
+    <t xml:space="preserve">Aysén</t>
   </si>
   <si>
     <t xml:space="preserve">11303</t>
@@ -79,9 +79,6 @@
     <t xml:space="preserve">11201</t>
   </si>
   <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11102</t>
   </si>
   <si>
@@ -160,7 +157,7 @@
     <t xml:space="preserve">Cabo de Hornos</t>
   </si>
   <si>
-    <t xml:space="preserve">Valparaiso</t>
+    <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
     <t xml:space="preserve">5702</t>
@@ -283,9 +280,6 @@
     <t xml:space="preserve">5101</t>
   </si>
   <si>
-    <t xml:space="preserve">Valparaíso</t>
-  </si>
-  <si>
     <t xml:space="preserve">5501</t>
   </si>
   <si>
@@ -442,7 +436,7 @@
     <t xml:space="preserve">Peñalolén</t>
   </si>
   <si>
-    <t xml:space="preserve">Nuble</t>
+    <t xml:space="preserve">Ñuble</t>
   </si>
   <si>
     <t xml:space="preserve">16304</t>
@@ -511,18 +505,18 @@
     <t xml:space="preserve">Villa Alegre</t>
   </si>
   <si>
+    <t xml:space="preserve">5803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olmué</t>
+  </si>
+  <si>
     <t xml:space="preserve">16106</t>
   </si>
   <si>
     <t xml:space="preserve">Pinto</t>
   </si>
   <si>
-    <t xml:space="preserve">5803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olmué</t>
-  </si>
-  <si>
     <t xml:space="preserve">13302</t>
   </si>
   <si>
@@ -1141,7 +1135,7 @@
     <t xml:space="preserve">Vitacura</t>
   </si>
   <si>
-    <t xml:space="preserve">Tarapaca</t>
+    <t xml:space="preserve">Tarapacá</t>
   </si>
   <si>
     <t xml:space="preserve">1404</t>
@@ -1390,7 +1384,7 @@
     <t xml:space="preserve">Camiña</t>
   </si>
   <si>
-    <t xml:space="preserve">Biobio</t>
+    <t xml:space="preserve">Biobío</t>
   </si>
   <si>
     <t xml:space="preserve">8314</t>
@@ -1414,7 +1408,7 @@
     <t xml:space="preserve">Puerto Octay</t>
   </si>
   <si>
-    <t xml:space="preserve">La Araucania</t>
+    <t xml:space="preserve">La Araucanía</t>
   </si>
   <si>
     <t xml:space="preserve">9113</t>
@@ -1537,7 +1531,7 @@
     <t xml:space="preserve">Chaitén</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Rios</t>
+    <t xml:space="preserve">Los Ríos</t>
   </si>
   <si>
     <t xml:space="preserve">14102</t>
@@ -1687,7 +1681,7 @@
     <t xml:space="preserve">8206</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">10101</t>
@@ -1855,7 +1849,7 @@
     <t xml:space="preserve">8301</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">8302</t>
@@ -2041,7 +2035,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:30</t>
+    <t xml:space="preserve">2026-10-05 18:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2573,7 +2567,7 @@
         <v>19</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>13</v>
@@ -2602,10 +2596,10 @@
         <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>13</v>
@@ -2634,10 +2628,10 @@
         <v>16</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>13</v>
@@ -2666,10 +2660,10 @@
         <v>16</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>13</v>
@@ -2698,10 +2692,10 @@
         <v>16</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>13</v>
@@ -2730,10 +2724,10 @@
         <v>16</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>13</v>
@@ -2762,10 +2756,10 @@
         <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>13</v>
@@ -2794,10 +2788,10 @@
         <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>13</v>
@@ -2826,10 +2820,10 @@
         <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>13</v>
@@ -2858,10 +2852,10 @@
         <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>13</v>
@@ -2890,10 +2884,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>13</v>
@@ -2922,10 +2916,10 @@
         <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>13</v>
@@ -2954,10 +2948,10 @@
         <v>16</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>13</v>
@@ -2986,10 +2980,10 @@
         <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>13</v>
@@ -3015,19 +3009,19 @@
         <v>5</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
@@ -3047,19 +3041,19 @@
         <v>13</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
@@ -3079,19 +3073,19 @@
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
@@ -3111,19 +3105,19 @@
         <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
@@ -3143,19 +3137,19 @@
         <v>5</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="F22" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
@@ -3175,19 +3169,19 @@
         <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="F23" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
@@ -3207,19 +3201,19 @@
         <v>13</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
@@ -3239,19 +3233,19 @@
         <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="F25" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
@@ -3271,19 +3265,19 @@
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="F26" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
@@ -3303,19 +3297,19 @@
         <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="F27" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
@@ -3335,19 +3329,19 @@
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="F28" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
@@ -3367,19 +3361,19 @@
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F29" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
@@ -3399,19 +3393,19 @@
         <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="F30" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
@@ -3431,19 +3425,19 @@
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="F31" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
@@ -3463,19 +3457,19 @@
         <v>13</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="F32" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
@@ -3495,19 +3489,19 @@
         <v>13</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="F33" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
@@ -3527,19 +3521,19 @@
         <v>13</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D34" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="F34" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
@@ -3559,19 +3553,19 @@
         <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
@@ -3591,19 +3585,19 @@
         <v>5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
@@ -3623,19 +3617,19 @@
         <v>13</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
@@ -3655,19 +3649,19 @@
         <v>6</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
@@ -3687,19 +3681,19 @@
         <v>13</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
@@ -3719,19 +3713,19 @@
         <v>13</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
@@ -3751,19 +3745,19 @@
         <v>13</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
@@ -3783,19 +3777,19 @@
         <v>13</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
@@ -3815,19 +3809,19 @@
         <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
@@ -3847,19 +3841,19 @@
         <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
@@ -3879,19 +3873,19 @@
         <v>13</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
@@ -3911,19 +3905,19 @@
         <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
@@ -3943,19 +3937,19 @@
         <v>5</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
@@ -3975,19 +3969,19 @@
         <v>5</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
@@ -4007,19 +4001,19 @@
         <v>6</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
@@ -4039,19 +4033,19 @@
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
@@ -4071,19 +4065,19 @@
         <v>13</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
@@ -4103,19 +4097,19 @@
         <v>5</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
@@ -4135,19 +4129,19 @@
         <v>6</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
@@ -4167,19 +4161,19 @@
         <v>13</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
@@ -4199,19 +4193,19 @@
         <v>13</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
@@ -4231,19 +4225,19 @@
         <v>5</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
@@ -4263,19 +4257,19 @@
         <v>13</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
@@ -4295,19 +4289,19 @@
         <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
@@ -4327,19 +4321,19 @@
         <v>6</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
@@ -4359,19 +4353,19 @@
         <v>6</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
@@ -4391,19 +4385,19 @@
         <v>13</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
@@ -4423,19 +4417,19 @@
         <v>16</v>
       </c>
       <c r="C62" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="F62" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
@@ -4455,19 +4449,19 @@
         <v>5</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
@@ -4487,19 +4481,19 @@
         <v>7</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
@@ -4519,19 +4513,19 @@
         <v>13</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
@@ -4551,19 +4545,19 @@
         <v>7</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
@@ -4583,19 +4577,19 @@
         <v>6</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
@@ -4615,19 +4609,19 @@
         <v>13</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
@@ -4647,19 +4641,19 @@
         <v>6</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
@@ -4679,19 +4673,19 @@
         <v>13</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
@@ -4711,19 +4705,19 @@
         <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
@@ -4743,19 +4737,19 @@
         <v>7</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
@@ -4772,22 +4766,22 @@
         <v>2022</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
@@ -4804,28 +4798,28 @@
         <v>2022</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>15</v>
@@ -4839,19 +4833,19 @@
         <v>13</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
@@ -4871,19 +4865,19 @@
         <v>16</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
@@ -4903,19 +4897,19 @@
         <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
@@ -4935,19 +4929,19 @@
         <v>5</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
@@ -4967,19 +4961,19 @@
         <v>7</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
@@ -4999,19 +4993,19 @@
         <v>7</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
@@ -5031,19 +5025,19 @@
         <v>6</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
@@ -5063,19 +5057,19 @@
         <v>5</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
@@ -5095,19 +5089,19 @@
         <v>16</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
@@ -5127,19 +5121,19 @@
         <v>13</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
@@ -5159,19 +5153,19 @@
         <v>5</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
@@ -5191,19 +5185,19 @@
         <v>13</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
@@ -5223,19 +5217,19 @@
         <v>5</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
@@ -5255,19 +5249,19 @@
         <v>7</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
@@ -5287,19 +5281,19 @@
         <v>5</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
@@ -5319,19 +5313,19 @@
         <v>16</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
@@ -5351,19 +5345,19 @@
         <v>13</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
@@ -5383,19 +5377,19 @@
         <v>6</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
@@ -5415,19 +5409,19 @@
         <v>6</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
@@ -5447,19 +5441,19 @@
         <v>5</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
@@ -5479,19 +5473,19 @@
         <v>6</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
@@ -5511,19 +5505,19 @@
         <v>13</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
@@ -5543,19 +5537,19 @@
         <v>7</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
@@ -5575,19 +5569,19 @@
         <v>7</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
@@ -5607,19 +5601,19 @@
         <v>13</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
@@ -5639,19 +5633,19 @@
         <v>13</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
@@ -5671,19 +5665,19 @@
         <v>13</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
@@ -5703,19 +5697,19 @@
         <v>6</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
@@ -5735,19 +5729,19 @@
         <v>6</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
@@ -5767,19 +5761,19 @@
         <v>16</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
@@ -5799,19 +5793,19 @@
         <v>5</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
@@ -5831,19 +5825,19 @@
         <v>6</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
@@ -5863,19 +5857,19 @@
         <v>5</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
@@ -5895,19 +5889,19 @@
         <v>13</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
@@ -5927,19 +5921,19 @@
         <v>7</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
@@ -5959,19 +5953,19 @@
         <v>5</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
@@ -5991,19 +5985,19 @@
         <v>6</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
@@ -6023,19 +6017,19 @@
         <v>7</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
@@ -6055,19 +6049,19 @@
         <v>16</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
@@ -6087,19 +6081,19 @@
         <v>13</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
@@ -6119,19 +6113,19 @@
         <v>6</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
@@ -6151,19 +6145,19 @@
         <v>16</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
@@ -6183,19 +6177,19 @@
         <v>7</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
@@ -6215,19 +6209,19 @@
         <v>7</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
@@ -6247,19 +6241,19 @@
         <v>6</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
@@ -6279,19 +6273,19 @@
         <v>6</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
@@ -6311,19 +6305,19 @@
         <v>13</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
@@ -6343,19 +6337,19 @@
         <v>6</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
@@ -6375,19 +6369,19 @@
         <v>16</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
@@ -6407,19 +6401,19 @@
         <v>7</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
@@ -6439,19 +6433,19 @@
         <v>6</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
@@ -6471,19 +6465,19 @@
         <v>7</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
@@ -6503,19 +6497,19 @@
         <v>7</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
@@ -6535,19 +6529,19 @@
         <v>6</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
@@ -6567,19 +6561,19 @@
         <v>6</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
@@ -6599,19 +6593,19 @@
         <v>13</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
@@ -6631,19 +6625,19 @@
         <v>7</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
@@ -6663,19 +6657,19 @@
         <v>7</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
@@ -6695,19 +6689,19 @@
         <v>16</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
@@ -6727,19 +6721,19 @@
         <v>5</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
@@ -6759,19 +6753,19 @@
         <v>16</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
@@ -6791,19 +6785,19 @@
         <v>13</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
@@ -6823,19 +6817,19 @@
         <v>6</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
@@ -6855,19 +6849,19 @@
         <v>7</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
@@ -6887,19 +6881,19 @@
         <v>5</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
@@ -6919,19 +6913,19 @@
         <v>5</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
@@ -6951,19 +6945,19 @@
         <v>5</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
@@ -6983,19 +6977,19 @@
         <v>13</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
@@ -7015,19 +7009,19 @@
         <v>13</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
@@ -7047,19 +7041,19 @@
         <v>16</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
@@ -7079,19 +7073,19 @@
         <v>7</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
@@ -7111,19 +7105,19 @@
         <v>5</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
@@ -7143,19 +7137,19 @@
         <v>6</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
@@ -7175,19 +7169,19 @@
         <v>5</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
@@ -7207,19 +7201,19 @@
         <v>13</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
@@ -7239,19 +7233,19 @@
         <v>13</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
@@ -7271,19 +7265,19 @@
         <v>16</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
@@ -7303,19 +7297,19 @@
         <v>5</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
@@ -7335,19 +7329,19 @@
         <v>7</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
@@ -7367,19 +7361,19 @@
         <v>6</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
@@ -7399,19 +7393,19 @@
         <v>13</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
@@ -7431,19 +7425,19 @@
         <v>6</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
@@ -7463,19 +7457,19 @@
         <v>7</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
@@ -7495,19 +7489,19 @@
         <v>13</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
@@ -7527,19 +7521,19 @@
         <v>6</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
@@ -7559,19 +7553,19 @@
         <v>7</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
@@ -7591,19 +7585,19 @@
         <v>16</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
@@ -7623,19 +7617,19 @@
         <v>13</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
@@ -7655,19 +7649,19 @@
         <v>16</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
@@ -7687,19 +7681,19 @@
         <v>16</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
@@ -7719,19 +7713,19 @@
         <v>13</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
@@ -7751,19 +7745,19 @@
         <v>13</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
@@ -7783,19 +7777,19 @@
         <v>6</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
@@ -7815,19 +7809,19 @@
         <v>13</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
@@ -7847,19 +7841,19 @@
         <v>6</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
@@ -7879,19 +7873,19 @@
         <v>6</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
@@ -7911,19 +7905,19 @@
         <v>16</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
@@ -7943,19 +7937,19 @@
         <v>16</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
@@ -7975,19 +7969,19 @@
         <v>13</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
@@ -8007,19 +8001,19 @@
         <v>16</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
@@ -8039,19 +8033,19 @@
         <v>5</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
@@ -8071,19 +8065,19 @@
         <v>13</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
@@ -8103,19 +8097,19 @@
         <v>13</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
@@ -8135,19 +8129,19 @@
         <v>1</v>
       </c>
       <c r="C178" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E178" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="D178" s="2" t="s">
+      <c r="F178" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="E178" s="2" t="s">
+      <c r="G178" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="F178" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="G178" s="2" t="s">
-        <v>378</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
@@ -8167,19 +8161,19 @@
         <v>3</v>
       </c>
       <c r="C179" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E179" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="D179" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="E179" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="F179" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
@@ -8199,19 +8193,19 @@
         <v>1</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
@@ -8231,19 +8225,19 @@
         <v>2</v>
       </c>
       <c r="C181" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E181" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="D181" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="E181" s="2" t="s">
-        <v>386</v>
-      </c>
       <c r="F181" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
@@ -8263,19 +8257,19 @@
         <v>2</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
@@ -8295,19 +8289,19 @@
         <v>4</v>
       </c>
       <c r="C183" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E183" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="D183" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="E183" s="2" t="s">
-        <v>391</v>
-      </c>
       <c r="F183" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
@@ -8327,19 +8321,19 @@
         <v>3</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
@@ -8359,19 +8353,19 @@
         <v>2</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
@@ -8391,19 +8385,19 @@
         <v>4</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
@@ -8423,19 +8417,19 @@
         <v>1</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
@@ -8455,19 +8449,19 @@
         <v>3</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
@@ -8487,19 +8481,19 @@
         <v>4</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
@@ -8519,19 +8513,19 @@
         <v>3</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
@@ -8551,19 +8545,19 @@
         <v>3</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
@@ -8583,19 +8577,19 @@
         <v>15</v>
       </c>
       <c r="C192" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E192" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="D192" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="E192" s="2" t="s">
-        <v>410</v>
-      </c>
       <c r="F192" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
@@ -8615,19 +8609,19 @@
         <v>2</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
@@ -8647,19 +8641,19 @@
         <v>2</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
@@ -8679,19 +8673,19 @@
         <v>4</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
@@ -8711,19 +8705,19 @@
         <v>1</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
@@ -8743,19 +8737,19 @@
         <v>4</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
@@ -8775,19 +8769,19 @@
         <v>3</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
@@ -8807,19 +8801,19 @@
         <v>4</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
@@ -8839,19 +8833,19 @@
         <v>4</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
@@ -8871,19 +8865,19 @@
         <v>2</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
@@ -8903,19 +8897,19 @@
         <v>15</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
@@ -8935,19 +8929,19 @@
         <v>4</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
@@ -8967,19 +8961,19 @@
         <v>4</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
@@ -8999,19 +8993,19 @@
         <v>3</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
@@ -9031,19 +9025,19 @@
         <v>3</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
@@ -9063,19 +9057,19 @@
         <v>4</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
@@ -9095,19 +9089,19 @@
         <v>3</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
@@ -9127,19 +9121,19 @@
         <v>4</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
@@ -9159,19 +9153,19 @@
         <v>4</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
@@ -9191,19 +9185,19 @@
         <v>4</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
@@ -9223,19 +9217,19 @@
         <v>4</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
@@ -9255,19 +9249,19 @@
         <v>2</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9287,19 +9281,19 @@
         <v>2</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9319,19 +9313,19 @@
         <v>4</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9351,19 +9345,19 @@
         <v>1</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9383,19 +9377,19 @@
         <v>8</v>
       </c>
       <c r="C217" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E217" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="D217" s="2" t="s">
+      <c r="F217" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="E217" s="2" t="s">
+      <c r="G217" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="F217" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="G217" s="2" t="s">
-        <v>461</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
@@ -9415,19 +9409,19 @@
         <v>10</v>
       </c>
       <c r="C218" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E218" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D218" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="E218" s="2" t="s">
-        <v>464</v>
-      </c>
       <c r="F218" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
@@ -9447,19 +9441,19 @@
         <v>9</v>
       </c>
       <c r="C219" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E219" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D219" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="E219" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="F219" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
@@ -9479,19 +9473,19 @@
         <v>10</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
@@ -9511,19 +9505,19 @@
         <v>9</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
@@ -9543,19 +9537,19 @@
         <v>8</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
@@ -9575,19 +9569,19 @@
         <v>10</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
@@ -9607,19 +9601,19 @@
         <v>10</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
@@ -9639,19 +9633,19 @@
         <v>10</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
@@ -9671,19 +9665,19 @@
         <v>10</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
@@ -9703,19 +9697,19 @@
         <v>10</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
@@ -9735,19 +9729,19 @@
         <v>10</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
@@ -9767,19 +9761,19 @@
         <v>8</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>
@@ -9799,19 +9793,19 @@
         <v>9</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>15</v>
@@ -9831,19 +9825,19 @@
         <v>10</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H231" s="2" t="s">
         <v>15</v>
@@ -9863,19 +9857,19 @@
         <v>10</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>15</v>
@@ -9895,19 +9889,19 @@
         <v>10</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>15</v>
@@ -9927,19 +9921,19 @@
         <v>10</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>15</v>
@@ -9959,19 +9953,19 @@
         <v>9</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>15</v>
@@ -9991,19 +9985,19 @@
         <v>10</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>15</v>
@@ -10023,19 +10017,19 @@
         <v>10</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>15</v>
@@ -10055,19 +10049,19 @@
         <v>10</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>15</v>
@@ -10087,19 +10081,19 @@
         <v>14</v>
       </c>
       <c r="C239" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E239" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="D239" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>508</v>
-      </c>
       <c r="F239" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>15</v>
@@ -10119,19 +10113,19 @@
         <v>9</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>15</v>
@@ -10151,19 +10145,19 @@
         <v>9</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>15</v>
@@ -10183,19 +10177,19 @@
         <v>14</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>15</v>
@@ -10215,19 +10209,19 @@
         <v>9</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H243" s="2" t="s">
         <v>15</v>
@@ -10247,19 +10241,19 @@
         <v>14</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>15</v>
@@ -10279,19 +10273,19 @@
         <v>8</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H245" s="2" t="s">
         <v>15</v>
@@ -10311,19 +10305,19 @@
         <v>10</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>15</v>
@@ -10343,19 +10337,19 @@
         <v>10</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H247" s="2" t="s">
         <v>15</v>
@@ -10375,19 +10369,19 @@
         <v>9</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>15</v>
@@ -10407,19 +10401,19 @@
         <v>8</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H249" s="2" t="s">
         <v>15</v>
@@ -10439,19 +10433,19 @@
         <v>8</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>15</v>
@@ -10471,19 +10465,19 @@
         <v>9</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>15</v>
@@ -10503,19 +10497,19 @@
         <v>10</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>15</v>
@@ -10535,19 +10529,19 @@
         <v>14</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>15</v>
@@ -10567,19 +10561,19 @@
         <v>8</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>15</v>
@@ -10599,19 +10593,19 @@
         <v>8</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>15</v>
@@ -10631,19 +10625,19 @@
         <v>10</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>15</v>
@@ -10663,19 +10657,19 @@
         <v>9</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>15</v>
@@ -10695,19 +10689,19 @@
         <v>10</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>15</v>
@@ -10727,19 +10721,19 @@
         <v>8</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H259" s="2" t="s">
         <v>15</v>
@@ -10759,19 +10753,19 @@
         <v>9</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>15</v>
@@ -10791,19 +10785,19 @@
         <v>9</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>15</v>
@@ -10823,19 +10817,19 @@
         <v>9</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>15</v>
@@ -10855,19 +10849,19 @@
         <v>8</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H263" s="2" t="s">
         <v>15</v>
@@ -10887,19 +10881,19 @@
         <v>10</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>15</v>
@@ -10919,19 +10913,19 @@
         <v>9</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H265" s="2" t="s">
         <v>15</v>
@@ -10951,19 +10945,19 @@
         <v>9</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>15</v>
@@ -10983,19 +10977,19 @@
         <v>8</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H267" s="2" t="s">
         <v>15</v>
@@ -11015,19 +11009,19 @@
         <v>10</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>15</v>
@@ -11047,19 +11041,19 @@
         <v>10</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H269" s="2" t="s">
         <v>15</v>
@@ -11079,19 +11073,19 @@
         <v>9</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>15</v>
@@ -11111,19 +11105,19 @@
         <v>9</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H271" s="2" t="s">
         <v>15</v>
@@ -11143,19 +11137,19 @@
         <v>9</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>15</v>
@@ -11175,19 +11169,19 @@
         <v>8</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>15</v>
@@ -11207,19 +11201,19 @@
         <v>9</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>15</v>
@@ -11239,19 +11233,19 @@
         <v>14</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>15</v>
@@ -11271,19 +11265,19 @@
         <v>9</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>15</v>
@@ -11303,19 +11297,19 @@
         <v>8</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H277" s="2" t="s">
         <v>15</v>
@@ -11335,19 +11329,19 @@
         <v>8</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>15</v>
@@ -11367,19 +11361,19 @@
         <v>9</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H279" s="2" t="s">
         <v>15</v>
@@ -11399,19 +11393,19 @@
         <v>8</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>15</v>
@@ -11431,19 +11425,19 @@
         <v>9</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G281" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H281" s="2" t="s">
         <v>15</v>
@@ -11463,19 +11457,19 @@
         <v>9</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>15</v>
@@ -11495,19 +11489,19 @@
         <v>8</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>15</v>
@@ -11527,19 +11521,19 @@
         <v>8</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>15</v>
@@ -11559,19 +11553,19 @@
         <v>9</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>15</v>
@@ -11591,19 +11585,19 @@
         <v>10</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>15</v>
@@ -11623,19 +11617,19 @@
         <v>10</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H287" s="2" t="s">
         <v>15</v>
@@ -11655,19 +11649,19 @@
         <v>10</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>15</v>
@@ -11687,19 +11681,19 @@
         <v>10</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G289" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H289" s="2" t="s">
         <v>15</v>
@@ -11719,19 +11713,19 @@
         <v>8</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>15</v>
@@ -11751,19 +11745,19 @@
         <v>8</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>15</v>
@@ -11783,19 +11777,19 @@
         <v>8</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>15</v>
@@ -11815,19 +11809,19 @@
         <v>8</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>15</v>
@@ -11847,19 +11841,19 @@
         <v>8</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>15</v>
@@ -11879,19 +11873,19 @@
         <v>8</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>15</v>
@@ -11911,19 +11905,19 @@
         <v>10</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>15</v>
@@ -11943,19 +11937,19 @@
         <v>9</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H297" s="2" t="s">
         <v>15</v>
@@ -11975,19 +11969,19 @@
         <v>8</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>15</v>
@@ -12007,19 +12001,19 @@
         <v>14</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H299" s="2" t="s">
         <v>15</v>
@@ -12039,19 +12033,19 @@
         <v>8</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>15</v>
@@ -12071,19 +12065,19 @@
         <v>10</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H301" s="2" t="s">
         <v>15</v>
@@ -12103,19 +12097,19 @@
         <v>9</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>15</v>
@@ -12135,19 +12129,19 @@
         <v>14</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>15</v>
@@ -12167,19 +12161,19 @@
         <v>9</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>15</v>
@@ -12199,19 +12193,19 @@
         <v>8</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H305" s="2" t="s">
         <v>15</v>
@@ -12231,19 +12225,19 @@
         <v>14</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>15</v>
@@ -12263,19 +12257,19 @@
         <v>9</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H307" s="2" t="s">
         <v>15</v>
@@ -12295,19 +12289,19 @@
         <v>8</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>15</v>
@@ -12327,19 +12321,19 @@
         <v>14</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H309" s="2" t="s">
         <v>15</v>
@@ -12359,19 +12353,19 @@
         <v>9</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>15</v>
@@ -12391,19 +12385,19 @@
         <v>9</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H311" s="2" t="s">
         <v>15</v>
@@ -12423,19 +12417,19 @@
         <v>10</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>15</v>
@@ -12455,19 +12449,19 @@
         <v>8</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>15</v>
@@ -12487,19 +12481,19 @@
         <v>14</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>15</v>
@@ -12519,19 +12513,19 @@
         <v>8</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H315" s="2" t="s">
         <v>15</v>
@@ -12551,19 +12545,19 @@
         <v>8</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>15</v>
@@ -12583,19 +12577,19 @@
         <v>9</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H317" s="2" t="s">
         <v>15</v>
@@ -12615,19 +12609,19 @@
         <v>8</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>15</v>
@@ -12647,19 +12641,19 @@
         <v>14</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H319" s="2" t="s">
         <v>15</v>
@@ -12679,19 +12673,19 @@
         <v>9</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>15</v>
@@ -12711,19 +12705,19 @@
         <v>8</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H321" s="2" t="s">
         <v>15</v>
@@ -12753,7 +12747,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
@@ -12761,50 +12755,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
   </sheetData>
@@ -12826,21 +12820,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -12849,7 +12843,7 @@
         <v>2022</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
   </sheetData>
